--- a/project/outputs_xlsx_solution/prog-loop.4-wide-NR-4.xlsx
+++ b/project/outputs_xlsx_solution/prog-loop.4-wide-NR-4.xlsx
@@ -606,12 +606,6 @@
       <c r="AJ1">
         <v>33</v>
       </c>
-      <c r="AK1">
-        <v>34</v>
-      </c>
-      <c r="AL1">
-        <v>35</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -929,12 +923,9 @@
         <v>22</v>
       </c>
       <c r="O12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q12" t="s">
         <v>21</v>
       </c>
     </row>
@@ -948,16 +939,16 @@
       <c r="C13" t="s">
         <v>8</v>
       </c>
+      <c r="P13" t="s">
+        <v>5</v>
+      </c>
       <c r="Q13" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R13" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="S13" t="s">
-        <v>14</v>
-      </c>
-      <c r="T13" t="s">
         <v>21</v>
       </c>
     </row>
@@ -971,14 +962,17 @@
       <c r="C14" t="s">
         <v>10</v>
       </c>
+      <c r="P14" t="s">
+        <v>5</v>
+      </c>
       <c r="Q14" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R14" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="S14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T14" t="s">
         <v>14</v>
@@ -990,9 +984,6 @@
         <v>14</v>
       </c>
       <c r="W14" t="s">
-        <v>14</v>
-      </c>
-      <c r="X14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1006,22 +997,22 @@
       <c r="C15" t="s">
         <v>11</v>
       </c>
+      <c r="P15" t="s">
+        <v>5</v>
+      </c>
       <c r="Q15" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R15" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="S15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T15" t="s">
-        <v>14</v>
-      </c>
-      <c r="U15" t="s">
         <v>20</v>
       </c>
-      <c r="X15" t="s">
+      <c r="W15" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1035,15 +1026,18 @@
       <c r="C16" t="s">
         <v>12</v>
       </c>
+      <c r="P16" t="s">
+        <v>5</v>
+      </c>
       <c r="Q16" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R16" t="s">
-        <v>9</v>
-      </c>
-      <c r="S16" t="s">
         <v>16</v>
       </c>
+      <c r="W16" t="s">
+        <v>14</v>
+      </c>
       <c r="X16" t="s">
         <v>14</v>
       </c>
@@ -1051,9 +1045,6 @@
         <v>14</v>
       </c>
       <c r="Z16" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA16" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1067,19 +1058,19 @@
       <c r="C17" t="s">
         <v>13</v>
       </c>
+      <c r="Q17" t="s">
+        <v>5</v>
+      </c>
       <c r="R17" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S17" t="s">
-        <v>9</v>
-      </c>
-      <c r="T17" t="s">
         <v>16</v>
       </c>
+      <c r="Z17" t="s">
+        <v>14</v>
+      </c>
       <c r="AA17" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB17" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1093,11 +1084,14 @@
       <c r="C18" t="s">
         <v>17</v>
       </c>
+      <c r="Q18" t="s">
+        <v>5</v>
+      </c>
       <c r="R18" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S18" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="T18" t="s">
         <v>22</v>
@@ -1109,15 +1103,12 @@
         <v>22</v>
       </c>
       <c r="W18" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="X18" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y18" t="s">
         <v>20</v>
       </c>
-      <c r="AB18" t="s">
+      <c r="AA18" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1131,22 +1122,22 @@
       <c r="C19" t="s">
         <v>18</v>
       </c>
+      <c r="Q19" t="s">
+        <v>5</v>
+      </c>
       <c r="R19" t="s">
-        <v>5</v>
-      </c>
-      <c r="S19" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="W19" t="s">
+        <v>15</v>
       </c>
       <c r="X19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y19" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z19" t="s">
         <v>20</v>
       </c>
-      <c r="AB19" t="s">
+      <c r="AA19" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1160,11 +1151,14 @@
       <c r="C20" t="s">
         <v>19</v>
       </c>
+      <c r="Q20" t="s">
+        <v>5</v>
+      </c>
       <c r="R20" t="s">
-        <v>5</v>
-      </c>
-      <c r="S20" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="W20" t="s">
+        <v>22</v>
       </c>
       <c r="X20" t="s">
         <v>22</v>
@@ -1173,15 +1167,9 @@
         <v>22</v>
       </c>
       <c r="Z20" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AA20" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC20" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1195,19 +1183,19 @@
       <c r="C21" t="s">
         <v>8</v>
       </c>
+      <c r="R21" t="s">
+        <v>5</v>
+      </c>
       <c r="S21" t="s">
-        <v>5</v>
-      </c>
-      <c r="T21" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>22</v>
       </c>
       <c r="AA21" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AB21" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC21" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1221,14 +1209,17 @@
       <c r="C22" t="s">
         <v>10</v>
       </c>
+      <c r="R22" t="s">
+        <v>5</v>
+      </c>
       <c r="S22" t="s">
-        <v>5</v>
-      </c>
-      <c r="T22" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>16</v>
       </c>
       <c r="AB22" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AC22" t="s">
         <v>14</v>
@@ -1240,9 +1231,6 @@
         <v>14</v>
       </c>
       <c r="AF22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG22" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1256,22 +1244,22 @@
       <c r="C23" t="s">
         <v>11</v>
       </c>
+      <c r="R23" t="s">
+        <v>5</v>
+      </c>
       <c r="S23" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>15</v>
       </c>
       <c r="AB23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC23" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD23" t="s">
         <v>20</v>
       </c>
-      <c r="AG23" t="s">
+      <c r="AF23" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1285,18 +1273,18 @@
       <c r="C24" t="s">
         <v>12</v>
       </c>
+      <c r="R24" t="s">
+        <v>5</v>
+      </c>
       <c r="S24" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB24" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC24" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA24" t="s">
         <v>16</v>
       </c>
+      <c r="AF24" t="s">
+        <v>14</v>
+      </c>
       <c r="AG24" t="s">
         <v>14</v>
       </c>
@@ -1304,9 +1292,6 @@
         <v>14</v>
       </c>
       <c r="AI24" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ24" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1320,19 +1305,19 @@
       <c r="C25" t="s">
         <v>13</v>
       </c>
+      <c r="S25" t="s">
+        <v>5</v>
+      </c>
       <c r="T25" t="s">
-        <v>5</v>
-      </c>
-      <c r="U25" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC25" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB25" t="s">
         <v>16</v>
       </c>
+      <c r="AI25" t="s">
+        <v>14</v>
+      </c>
       <c r="AJ25" t="s">
-        <v>14</v>
-      </c>
-      <c r="AK25" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1346,11 +1331,14 @@
       <c r="C26" t="s">
         <v>17</v>
       </c>
+      <c r="S26" t="s">
+        <v>5</v>
+      </c>
       <c r="T26" t="s">
-        <v>5</v>
-      </c>
-      <c r="U26" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>22</v>
       </c>
       <c r="AC26" t="s">
         <v>22</v>
@@ -1362,15 +1350,12 @@
         <v>22</v>
       </c>
       <c r="AF26" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AG26" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH26" t="s">
         <v>20</v>
       </c>
-      <c r="AK26" t="s">
+      <c r="AJ26" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1384,22 +1369,22 @@
       <c r="C27" t="s">
         <v>18</v>
       </c>
+      <c r="S27" t="s">
+        <v>5</v>
+      </c>
       <c r="T27" t="s">
-        <v>5</v>
-      </c>
-      <c r="U27" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>15</v>
       </c>
       <c r="AG27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH27" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI27" t="s">
         <v>20</v>
       </c>
-      <c r="AK27" t="s">
+      <c r="AJ27" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1413,11 +1398,14 @@
       <c r="C28" t="s">
         <v>19</v>
       </c>
+      <c r="S28" t="s">
+        <v>5</v>
+      </c>
       <c r="T28" t="s">
-        <v>5</v>
-      </c>
-      <c r="U28" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AF28" t="s">
+        <v>22</v>
       </c>
       <c r="AG28" t="s">
         <v>22</v>
@@ -1426,15 +1414,9 @@
         <v>22</v>
       </c>
       <c r="AI28" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AJ28" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK28" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL28" t="s">
         <v>21</v>
       </c>
     </row>
